--- a/data/trans_bre/IP2005-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 12,17</t>
+          <t>-7,06; 12,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 8,0</t>
+          <t>-11,67; 7,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 10,92</t>
+          <t>0,95; 11,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 4,32</t>
+          <t>-4,69; 3,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 14,61</t>
+          <t>-7,42; 14,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 9,27</t>
+          <t>-12,55; 8,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 12,25</t>
+          <t>0,96; 12,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 4,56</t>
+          <t>-4,73; 4,18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 9,6</t>
+          <t>-7,45; 9,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 10,1</t>
+          <t>-5,33; 9,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 14,48</t>
+          <t>1,98; 13,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 18,81</t>
+          <t>-2,24; 18,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 12,13</t>
+          <t>-8,74; 11,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 12,18</t>
+          <t>-5,82; 11,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 17,62</t>
+          <t>2,11; 15,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 25,57</t>
+          <t>-2,79; 26,5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 5,5</t>
+          <t>-4,59; 5,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 1,25</t>
+          <t>-11,74; 1,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 5,43</t>
+          <t>-6,01; 5,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 11,89</t>
+          <t>-8,8; 12,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 5,86</t>
+          <t>-4,63; 5,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 1,34</t>
+          <t>-12,17; 1,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 5,85</t>
+          <t>-6,31; 5,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 14,86</t>
+          <t>-9,57; 15,18</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 4,28</t>
+          <t>-5,82; 4,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 5,92</t>
+          <t>-11,7; 5,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 12,33</t>
+          <t>-4,9; 12,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,8; 4,71</t>
+          <t>-22,82; 4,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 4,61</t>
+          <t>-5,9; 4,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 6,93</t>
+          <t>-12,63; 7,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 15,52</t>
+          <t>-5,41; 15,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,15; 6,48</t>
+          <t>-26,64; 5,63</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 13,16</t>
+          <t>-16,02; 13,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 9,74</t>
+          <t>-15,67; 8,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 21,23</t>
+          <t>-5,19; 21,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 10,22</t>
+          <t>-7,4; 9,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 17,76</t>
+          <t>-17,54; 17,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 11,61</t>
+          <t>-16,72; 10,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 29,56</t>
+          <t>-5,62; 30,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 11,77</t>
+          <t>-7,79; 10,36</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 0,7</t>
+          <t>-11,26; 1,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,07; 20,59</t>
+          <t>0,69; 20,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,25; -1,54</t>
+          <t>-15,16; -1,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 1,52</t>
+          <t>-14,89; 1,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 0,7</t>
+          <t>-11,36; 1,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,09; 27,01</t>
+          <t>0,78; 27,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,25; -1,54</t>
+          <t>-15,16; -1,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 1,63</t>
+          <t>-15,33; 1,48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 5,64</t>
+          <t>-7,14; 5,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 2,62</t>
+          <t>-8,46; 2,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 6,56</t>
+          <t>-2,69; 6,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 11,44</t>
+          <t>-5,3; 10,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 6,63</t>
+          <t>-7,8; 6,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 2,78</t>
+          <t>-8,77; 2,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 7,32</t>
+          <t>-2,85; 7,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 14,83</t>
+          <t>-6,12; 14,23</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 7,24</t>
+          <t>-6,19; 7,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 4,53</t>
+          <t>-5,65; 4,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 4,64</t>
+          <t>-6,58; 4,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 0,17</t>
+          <t>-9,07; -0,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 8,96</t>
+          <t>-7,17; 9,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 5,05</t>
+          <t>-6,03; 5,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 5,46</t>
+          <t>-7,2; 5,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 0,17</t>
+          <t>-9,33; -0,42</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 2,81</t>
+          <t>-2,93; 2,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 1,82</t>
+          <t>-3,19; 2,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 4,45</t>
+          <t>-0,29; 4,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,84</t>
+          <t>-3,25; 3,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 3,21</t>
+          <t>-3,22; 2,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 2,04</t>
+          <t>-3,47; 2,52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 5,0</t>
+          <t>-0,3; 5,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 3,3</t>
+          <t>-3,64; 3,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2005-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 12,13</t>
+          <t>-6,5; 11,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 7,28</t>
+          <t>-13,27; 7,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 11,19</t>
+          <t>0,97; 11,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 3,98</t>
+          <t>-3,7; 4,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 14,66</t>
+          <t>-6,82; 14,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 8,78</t>
+          <t>-14,23; 8,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 12,6</t>
+          <t>0,98; 12,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 4,18</t>
+          <t>-3,74; 4,77</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 9,32</t>
+          <t>-7,27; 9,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 9,69</t>
+          <t>-4,59; 9,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 13,33</t>
+          <t>2,35; 13,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 18,88</t>
+          <t>-2,02; 18,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 11,83</t>
+          <t>-8,5; 11,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 11,84</t>
+          <t>-5,11; 11,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 15,49</t>
+          <t>2,81; 16,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 26,5</t>
+          <t>-2,45; 25,41</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 5,16</t>
+          <t>-5,35; 5,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 1,33</t>
+          <t>-11,34; 1,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 5,55</t>
+          <t>-6,74; 5,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 12,08</t>
+          <t>-8,03; 12,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 5,58</t>
+          <t>-5,35; 5,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 1,37</t>
+          <t>-11,62; 1,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 5,96</t>
+          <t>-6,95; 5,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 15,18</t>
+          <t>-8,81; 15,38</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 4,28</t>
+          <t>-5,67; 4,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 5,91</t>
+          <t>-12,13; 5,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 12,44</t>
+          <t>-4,78; 12,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 4,31</t>
+          <t>-21,9; 4,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 4,58</t>
+          <t>-5,76; 4,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 7,03</t>
+          <t>-13,14; 6,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 15,47</t>
+          <t>-5,25; 16,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,64; 5,63</t>
+          <t>-24,93; 6,27</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 13,45</t>
+          <t>-14,8; 15,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 8,48</t>
+          <t>-13,99; 9,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 21,59</t>
+          <t>-6,06; 20,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 9,09</t>
+          <t>-7,0; 8,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 17,64</t>
+          <t>-16,59; 20,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 10,29</t>
+          <t>-15,12; 11,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 30,42</t>
+          <t>-6,68; 28,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 10,36</t>
+          <t>-7,44; 10,41</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 1,65</t>
+          <t>-11,44; 0,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 20,69</t>
+          <t>0,22; 20,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,16; -1,52</t>
+          <t>-15,22; -1,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 1,49</t>
+          <t>-15,2; 1,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 1,72</t>
+          <t>-11,51; 0,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 27,6</t>
+          <t>0,57; 27,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,16; -1,52</t>
+          <t>-15,22; -1,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,33; 1,48</t>
+          <t>-15,73; 1,02</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 5,42</t>
+          <t>-6,78; 5,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 2,49</t>
+          <t>-7,7; 3,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 6,58</t>
+          <t>-2,46; 7,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 10,84</t>
+          <t>-5,52; 11,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 6,27</t>
+          <t>-7,35; 6,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 2,72</t>
+          <t>-8,18; 3,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 7,26</t>
+          <t>-2,54; 7,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 14,23</t>
+          <t>-6,4; 14,48</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 7,17</t>
+          <t>-6,79; 7,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 4,57</t>
+          <t>-5,7; 4,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 4,48</t>
+          <t>-7,4; 4,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,07; -0,41</t>
+          <t>-8,89; 0,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 9,01</t>
+          <t>-7,81; 8,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 5,15</t>
+          <t>-6,06; 4,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 5,12</t>
+          <t>-8,04; 5,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,33; -0,42</t>
+          <t>-9,21; -0,03</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 2,51</t>
+          <t>-2,66; 2,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,24</t>
+          <t>-3,37; 2,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,47</t>
+          <t>-0,34; 4,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 3,26</t>
+          <t>-3,24; 3,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 2,83</t>
+          <t>-2,95; 3,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 2,52</t>
+          <t>-3,65; 2,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 5,04</t>
+          <t>-0,37; 5,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 3,77</t>
+          <t>-3,68; 3,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2005-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,13%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 11,64</t>
+          <t>-6,8; 12,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 7,4</t>
+          <t>-12,29; 8,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 11,19</t>
+          <t>0,97; 10,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 4,5</t>
+          <t>-4,68; 4,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 14,1</t>
+          <t>-7,32; 14,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 8,69</t>
+          <t>-12,95; 9,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 12,6</t>
+          <t>0,98; 12,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 4,77</t>
+          <t>-4,75; 4,74</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,26</t>
+          <t>5,01</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 9,2</t>
+          <t>-7,23; 9,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 9,57</t>
+          <t>-5,65; 10,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 13,97</t>
+          <t>2,83; 14,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 18,3</t>
+          <t>-5,52; 14,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 11,72</t>
+          <t>-8,1; 12,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 11,58</t>
+          <t>-6,13; 12,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 16,63</t>
+          <t>3,13; 17,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 25,41</t>
+          <t>-6,62; 20,29</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 5,03</t>
+          <t>-4,72; 5,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 1,55</t>
+          <t>-12,24; 1,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 5,5</t>
+          <t>-6,78; 5,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 12,23</t>
+          <t>-8,95; 10,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 5,43</t>
+          <t>-4,85; 5,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 1,6</t>
+          <t>-12,58; 1,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 5,89</t>
+          <t>-6,98; 5,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 15,38</t>
+          <t>-10,02; 12,54</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-9,12</t>
+          <t>-8,26</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-11,19%</t>
+          <t>-10,2%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 4,32</t>
+          <t>-5,69; 4,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 5,7</t>
+          <t>-11,94; 5,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 12,87</t>
+          <t>-5,3; 12,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,9; 4,69</t>
+          <t>-22,19; 5,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 4,69</t>
+          <t>-5,8; 4,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 6,44</t>
+          <t>-12,82; 6,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 16,11</t>
+          <t>-5,72; 15,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,93; 6,27</t>
+          <t>-25,36; 7,94</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,75</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 15,55</t>
+          <t>-14,24; 13,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 9,11</t>
+          <t>-15,0; 9,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 20,32</t>
+          <t>-4,8; 21,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 8,91</t>
+          <t>-5,71; 10,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 20,96</t>
+          <t>-16,04; 17,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 11,18</t>
+          <t>-16,13; 11,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 28,17</t>
+          <t>-5,5; 29,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 10,41</t>
+          <t>-6,03; 12,72</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-6,11</t>
+          <t>-6,66</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-6,35%</t>
+          <t>-6,93%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 0,84</t>
+          <t>-11,53; 0,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,22; 20,13</t>
+          <t>0,07; 20,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,22; -1,56</t>
+          <t>-16,25; -1,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 1,09</t>
+          <t>-15,49; 1,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 0,86</t>
+          <t>-11,69; 0,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 27,43</t>
+          <t>0,09; 27,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,22; -1,56</t>
+          <t>-16,25; -1,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 1,02</t>
+          <t>-15,92; 1,25</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,16</t>
+          <t>3,48</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 5,49</t>
+          <t>-6,32; 5,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 3,13</t>
+          <t>-8,36; 2,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 7,1</t>
+          <t>-3,07; 6,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 11,01</t>
+          <t>-5,08; 11,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 6,45</t>
+          <t>-6,93; 6,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 3,34</t>
+          <t>-8,64; 2,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 7,94</t>
+          <t>-3,22; 7,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 14,48</t>
+          <t>-5,99; 15,67</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-4,47</t>
+          <t>-4,55</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-4,63%</t>
+          <t>-4,69%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 7,01</t>
+          <t>-5,97; 7,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 4,34</t>
+          <t>-5,81; 4,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 4,58</t>
+          <t>-7,16; 4,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 0,03</t>
+          <t>-9,59; -0,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 8,66</t>
+          <t>-6,87; 8,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 4,87</t>
+          <t>-6,22; 5,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 5,36</t>
+          <t>-7,75; 5,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,21; -0,03</t>
+          <t>-9,77; -0,21</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,74</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-0,2%</t>
+          <t>-0,84%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,69</t>
+          <t>-2,92; 2,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 2,0</t>
+          <t>-3,24; 1,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 4,7</t>
+          <t>-0,36; 4,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 3,13</t>
+          <t>-4,32; 2,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 3,09</t>
+          <t>-3,27; 3,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 2,23</t>
+          <t>-3,53; 2,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 5,25</t>
+          <t>-0,34; 5,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 3,65</t>
+          <t>-4,8; 2,63</t>
         </is>
       </c>
     </row>
